--- a/その他イベント一覧.xlsx
+++ b/その他イベント一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayur\OneDrive\デスクトップ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D88455F8-F34B-47D3-A849-C72200A1D216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010F5D5D-26BA-45AB-A4A4-AD89F9DDB85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{05EDD859-068E-4865-AA8A-16DF4353B232}"/>
+    <workbookView xWindow="13700" yWindow="3260" windowWidth="8840" windowHeight="10690" xr2:uid="{05EDD859-068E-4865-AA8A-16DF4353B232}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
   <si>
     <t>同盟争覇戦</t>
     <phoneticPr fontId="1"/>
@@ -730,6 +730,9 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
@@ -738,6 +741,9 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
@@ -757,6 +763,9 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
@@ -765,6 +774,9 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
@@ -773,6 +785,9 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
       <c r="B10" t="s">
         <v>18</v>
       </c>
@@ -792,6 +807,9 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
       <c r="B14" t="s">
         <v>22</v>
       </c>
@@ -800,6 +818,9 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
       <c r="B15" t="s">
         <v>23</v>
       </c>
@@ -808,6 +829,9 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
       <c r="B16" t="s">
         <v>24</v>
       </c>
@@ -815,7 +839,10 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
@@ -823,7 +850,10 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
@@ -831,7 +861,10 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
@@ -839,7 +872,10 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
       <c r="B20" t="s">
         <v>27</v>
       </c>
@@ -847,7 +883,10 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
       <c r="B21" t="s">
         <v>17</v>
       </c>
@@ -855,7 +894,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
@@ -863,7 +905,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
       <c r="B23" t="s">
         <v>39</v>
       </c>
@@ -871,12 +916,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
       <c r="B24" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
       <c r="B25" t="s">
         <v>29</v>
       </c>

--- a/その他イベント一覧.xlsx
+++ b/その他イベント一覧.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayur\OneDrive\デスクトップ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayur\OneDrive\デスクトップ\my_app\260510 manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010F5D5D-26BA-45AB-A4A4-AD89F9DDB85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8A18CF-61DE-424E-BD41-C29B1D79A8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13700" yWindow="3260" windowWidth="8840" windowHeight="10690" xr2:uid="{05EDD859-068E-4865-AA8A-16DF4353B232}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{05EDD859-068E-4865-AA8A-16DF4353B232}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
   <si>
     <t>同盟争覇戦</t>
     <phoneticPr fontId="1"/>
@@ -314,6 +314,13 @@
     </rPh>
     <rPh sb="6" eb="7">
       <t>ノチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>観光シアター</t>
+    <rPh sb="0" eb="2">
+      <t>カンコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -699,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6819F9C2-D2AE-4BE4-989A-BBD9E76E96A6}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20.4140625" customWidth="1"/>
@@ -822,10 +829,7 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -833,10 +837,10 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -844,10 +848,10 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -855,10 +859,10 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -866,10 +870,10 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -877,7 +881,7 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
@@ -888,10 +892,10 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -899,10 +903,10 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -910,10 +914,10 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -921,7 +925,10 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -929,9 +936,17 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
         <v>29</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>36</v>
       </c>
     </row>

--- a/その他イベント一覧.xlsx
+++ b/その他イベント一覧.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayur\OneDrive\デスクトップ\my_app\260510 manual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayur\OneDrive\デスクトップ\めも\my_app\260510 manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8A18CF-61DE-424E-BD41-C29B1D79A8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85E7104-0983-4BC3-9828-32DC9B4A4DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{05EDD859-068E-4865-AA8A-16DF4353B232}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="45">
   <si>
     <t>同盟争覇戦</t>
     <phoneticPr fontId="1"/>
@@ -322,6 +322,10 @@
     <rPh sb="0" eb="2">
       <t>カンコウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーロラホップ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -706,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6819F9C2-D2AE-4BE4-989A-BBD9E76E96A6}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20.4140625" customWidth="1"/>
@@ -950,6 +954,14 @@
         <v>36</v>
       </c>
     </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
